--- a/fx-server/资源/题库/样式.xlsx
+++ b/fx-server/资源/题库/样式.xlsx
@@ -123,7 +123,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -145,12 +145,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1200%%200%%true%%0xffffff00%%%%Microsoft YaHei%%32%%false%%false%%false%%false%%左对齐%%50%%0</t>
+          <t>200%%200%%1200%%200%%true%%0xffffff00%%%%Microsoft YaHei%%24%%false%%false%%false%%false%%左对齐%%50%%0</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -167,29 +167,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1200%%200%%true%%0xffffff00%%%%Microsoft YaHei%%32%%false%%false%%false%%false%%左对齐%%50%%0</t>
+          <t>500%%200%%1000%%500%%true%%0xffffff00%%%%Microsoft YaHei%%32%%false%%false%%false%%false%%左对齐%%50%%0</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>200%%600%%1000%%30%%true%%0x1a4d4dff%%%%Dialog%%36%%false%%false%%false%%false%%左对齐%%0</t>
+          <t>100%%100%%1000%%500%%true%%0x1a4d4dff%%%%Dialog%%36%%false%%false%%false%%false%%左对齐%%0</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>300%%50%%300%%50%%true%%0xffcc66ff%%E:\Income\202401\competition-app\fx-server\资源\按钮\2.png%%华文楷体%%24%%false%%true%%false%%false%%居中对齐%%10</t>
+          <t>300%%50%%300%%50%%true%%0xffcc66ff%%E:\Income\202401\competition-app\fx-server\资源\按钮\2.png%%华文楷体%%24%%false%%true%%false%%false%%居中对齐%%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -211,7 +211,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -233,7 +233,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -255,7 +255,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -277,7 +277,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -299,7 +299,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -321,7 +321,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -343,7 +343,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -365,7 +365,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -378,12 +378,16 @@
           <t>200%%600%%1000%%30%%true%%0x1a4d4dff%%%%Dialog%%36%%false%%false%%false%%false%%左对齐%%0</t>
         </is>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>100%%100%%100%%100%%false%%0xffffffff%%%%System Regular%%12%%false%%false%%false%%false%%null%%</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -401,7 +405,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -419,7 +423,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -437,7 +441,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -455,7 +459,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -473,7 +477,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -491,7 +495,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -509,7 +513,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -527,7 +531,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -545,7 +549,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -581,7 +585,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -599,7 +603,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -617,7 +621,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -635,7 +639,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -653,7 +657,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -671,7 +675,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -689,7 +693,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -707,7 +711,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -725,7 +729,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -739,7 +743,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -753,7 +757,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -767,7 +771,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -781,7 +785,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -795,7 +799,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -809,7 +813,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -823,7 +827,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -837,7 +841,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -851,7 +855,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -865,7 +869,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -879,7 +883,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -893,7 +897,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -907,7 +911,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -921,7 +925,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -935,7 +939,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -949,7 +953,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -963,7 +967,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -977,7 +981,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -991,7 +995,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -1005,7 +1009,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -1019,7 +1023,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -1033,7 +1037,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -1047,7 +1051,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -1061,7 +1065,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -1075,7 +1079,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -1089,7 +1093,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -1103,7 +1107,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -1121,7 +1125,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -1135,7 +1139,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -1149,7 +1153,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -1163,7 +1167,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -1177,7 +1181,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -1191,7 +1195,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -1205,7 +1209,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -1219,7 +1223,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -1233,7 +1237,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -1247,7 +1251,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -1261,7 +1265,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -1275,7 +1279,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -1289,7 +1293,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -1303,7 +1307,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -1317,7 +1321,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -1331,7 +1335,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -1345,7 +1349,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -1359,7 +1363,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -1373,7 +1377,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -1387,7 +1391,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -1401,7 +1405,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -1415,7 +1419,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -1429,7 +1433,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -1443,7 +1447,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -1457,7 +1461,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -1471,7 +1475,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -1485,7 +1489,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -1499,7 +1503,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -1513,7 +1517,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -1527,7 +1531,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">

--- a/fx-server/资源/题库/样式.xlsx
+++ b/fx-server/资源/题库/样式.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1200%%200%%true%%0xffffff00%%%%Microsoft YaHei%%28%%false%%false%%false%%false%%左对齐%%50%%0</t>
+          <t>200%%200%%1200%%200%%false%%0xffcc80ff%%%%Microsoft YaHei%%28%%false%%false%%false%%false%%左对齐%%50%%0</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>200%%200%%1200%%200%%true%%0xffffff00%%%%Microsoft YaHei%%28%%false%%false%%false%%false%%左对齐%%50%%0</t>
+          <t>200%%200%%120%%200%%true%%0xffffff00%%%%Microsoft YaHei%%28%%false%%false%%false%%false%%左对齐%%50%%0</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
